--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/antofagasta.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>881-414-CM25</t>
+          <t>3149-221-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>30171.93</v>
+        <v>20066.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3053-62-CM25</t>
+          <t>881-414-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>Gobierno Regional de Antofagasta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>26080.72</v>
+        <v>30171.93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2429-3087-CM25</t>
+          <t>3053-62-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>30476.52</v>
+        <v>26080.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1301865-1-CM26</t>
+          <t>2429-3087-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,32 +737,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>99802.92</v>
+        <v>30476.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3506-21-CM26</t>
+          <t>1301865-1-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -777,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -787,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -802,28 +798,32 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>77968.8</v>
+        <v>99802.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3834-43-CM26</t>
+          <t>3506-21-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,27 +833,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -863,12 +863,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>37961</v>
+        <v>77968.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2385-237-CM26</t>
+          <t>3834-43-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1479.41</v>
+        <v>37961</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2429-405-CM26</t>
+          <t>2385-237-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5273.5</v>
+        <v>1479.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2429-441-CM26</t>
+          <t>2429-405-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>38086.37</v>
+        <v>5273.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3149-202-CM26</t>
+          <t>2429-441-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>20049.95</v>
+        <v>38086.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3146-39-CM26</t>
+          <t>3149-202-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>20049.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3149-218-CM26</t>
+          <t>3146-39-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,6 +1244,67 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
+        <v>8255.860000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3149-218-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.253.600-2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
         <v>8436.98</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/antofagasta.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/antofagasta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3149-221-CM25</t>
+          <t>3506-18-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>20066.14</v>
+        <v>82755.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>881-414-CM25</t>
+          <t>3834-54-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>30171.93</v>
+        <v>34510</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3053-62-CM25</t>
+          <t>2385-348-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26080.72</v>
+        <v>1692.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2429-3087-CM25</t>
+          <t>1375735-46-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>30476.52</v>
+        <v>11186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1301865-1-CM26</t>
+          <t>3149-221-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,32 +798,28 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>99802.92</v>
+        <v>20066.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3506-21-CM26</t>
+          <t>2429-2562-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -848,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -863,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -878,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>77968.8</v>
+        <v>8205.219999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3834-43-CM26</t>
+          <t>2429-2563-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -939,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>37961</v>
+        <v>29304.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2385-237-CM26</t>
+          <t>881-414-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -970,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Gobierno Regional de Antofagasta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1479.41</v>
+        <v>30171.93</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2429-405-CM26</t>
+          <t>3053-62-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5273.5</v>
+        <v>26080.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2429-441-CM26</t>
+          <t>2429-3087-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,17 +1073,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1107,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>38086.37</v>
+        <v>30476.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3149-202-CM26</t>
+          <t>1301865-1-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>Corporación Municipal Desarrollo Social Antofagast</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,28 +1164,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>20049.95</v>
+        <v>99802.92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3146-39-CM26</t>
+          <t>3506-21-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8255.860000000001</v>
+        <v>77968.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3149-218-CM26</t>
+          <t>3834-43-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,27 +1260,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,7 +1305,434 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
+        <v>37961</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2385-237-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>1479.41</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2429-405-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>5273.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2429-441-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>38086.37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3149-202-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.253.600-2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>20049.95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3146-39-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.253.600-2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>8255.860000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3149-218-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.253.600-2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>8436.98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>881-232-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>72.224.100-2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Site Chile Sociedad Anónima</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.988.790-8</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>1547</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/antofagasta.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1733,6 +1733,67 @@
       </c>
       <c r="M21" s="2" t="n">
         <v>1547</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2429-1124-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>35154.5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/antofagasta.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/antofagasta.xlsx
@@ -562,7 +562,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1277,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1594,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1659,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1724,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1850,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
